--- a/models/sovereigns/Iraq_Sovereign_Model.xlsx
+++ b/models/sovereigns/Iraq_Sovereign_Model.xlsx
@@ -736,16 +736,34 @@
           <t>gov_debt_pct_gdp</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n"/>
+      <c r="B8" s="2" t="n">
+        <v>61.7</v>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -770,16 +788,34 @@
           <t>fiscal_balance_pct_gdp</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n"/>
+      <c r="B10" s="2" t="n">
+        <v>-7.9</v>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -838,16 +874,34 @@
           <t>current_account_pct_gdp</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n"/>
+      <c r="B14" s="2" t="n">
+        <v>-5.3</v>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -855,16 +909,34 @@
           <t>fdi_net_pct_gdp</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n"/>
+      <c r="B15" s="2" t="n">
+        <v>-2.995</v>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>World Bank WDI</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1006,16 +1078,34 @@
           <t>nominal_gdp_usd_bn</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n"/>
+      <c r="B22" s="2" t="n">
+        <v>264.784</v>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
           <t>USD bn</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">

--- a/models/sovereigns/Iraq_Sovereign_Model.xlsx
+++ b/models/sovereigns/Iraq_Sovereign_Model.xlsx
@@ -671,16 +671,34 @@
           <t>cpi_latest_yoy_pct</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
+      <c r="B5" s="2" t="n">
+        <v>3.0928</v>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>IMF CPI database</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>IMF CPI database, all items, y/y % change, monthly (auto-filled; a run's sourced point replaces it unless older)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -703,7 +721,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IMF</t>
+          <t>IMF Projections</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -737,7 +755,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>61.7</v>
+        <v>53.9</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -746,22 +764,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026E</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IMF WEO</t>
+          <t>IMF / Ministry of Finance</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>31-Jul-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+          <t>Total public debt to GDP</t>
         </is>
       </c>
     </row>
@@ -789,7 +807,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>-7.9</v>
+        <v>-4.2</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -798,24 +816,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026E</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IMF WEO</t>
+          <t>IMF Article IV</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
-        </is>
-      </c>
+          <t>20-May-25</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -969,7 +983,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>gross official FX reserves; $97.4bn end-2025</t>
+          <t>CBI gross official foreign exchange reserves</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1025,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Central Bank of Iraq</t>
+          <t>Central Bank of Iraq / IMF</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1114,7 +1128,7 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>0.506</v>
+        <v>0.50625</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1123,24 +1137,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>Oct-26</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Bondblox / Luxembourg Stock Exchange</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>08-Oct-26</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>LuxSE / Bondblox</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>single amortising 5.80% 2028</t>
-        </is>
-      </c>
+      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1289,7 +1299,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>None (Article IV / Post-Financing Assessment)</t>
+          <t>None active (Article IV surveillance and Post-Financing Assessment only; last SBA expired 2018)</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1318,15 +1328,20 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2026E</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -1340,7 +1355,8 @@
       </c>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="2" t="n"/>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1349,10 +1365,15 @@
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n">
         <v>-6.8</v>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>IMF Projections, 20-May-25</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1362,7 +1383,8 @@
       </c>
       <c r="B4" s="2" t="n"/>
       <c r="C4" s="2" t="n"/>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1372,7 +1394,8 @@
       </c>
       <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="n"/>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1380,9 +1403,16 @@
           <t>fiscal_balance_pct_gdp</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n"/>
+      <c r="B6" s="2" t="n">
+        <v>-4.2</v>
+      </c>
       <c r="C6" s="2" t="n"/>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>IMF Article IV, 20-May-25</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1392,7 +1422,8 @@
       </c>
       <c r="B7" s="2" t="n"/>
       <c r="C7" s="2" t="n"/>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1401,8 +1432,17 @@
         </is>
       </c>
       <c r="B8" s="2" t="n"/>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" t="inlineStr"/>
+      <c r="C8" s="2" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>IMF / Ministry of Finance, 31-Jul-26 (2026E is a year-end projection)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1412,7 +1452,8 @@
       </c>
       <c r="B9" s="2" t="n"/>
       <c r="C9" s="2" t="n"/>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1420,11 +1461,16 @@
           <t>gross_reserves_usd_bn</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n">
         <v>97.40000000000001</v>
       </c>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Central Bank of Iraq, 31-Jul-26 (end-2025 level)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1434,7 +1480,8 @@
       </c>
       <c r="B11" s="2" t="n"/>
       <c r="C11" s="2" t="n"/>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1444,7 +1491,8 @@
       </c>
       <c r="B12" s="2" t="n"/>
       <c r="C12" s="2" t="n"/>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/models/sovereigns/Iraq_Sovereign_Model.xlsx
+++ b/models/sovereigns/Iraq_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 08-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/iraq.json</t>
+          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/iraq.json</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IMF Projections</t>
+          <t>IMF projections (as cited in adjudicated document)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>53.9</v>
+        <v>57</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026E</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Total public debt to GDP</t>
+          <t>Total public debt, projected year-end 2026 (approx.)</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bondblox / Luxembourg Stock Exchange</t>
+          <t>Luxembourg Stock Exchange / Bondblox</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>None active (Article IV surveillance and Post-Financing Assessment only; last SBA expired 2018)</t>
+          <t>None (Article IV surveillance and Post-Financing Assessment; last SBA expired 2018)</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>IMF Projections, 20-May-25</t>
+          <t>IMF projections, 20-May-25</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IMF / Ministry of Finance, 31-Jul-26 (2026E is a year-end projection)</t>
+          <t>IMF / Ministry of Finance, 31-Jul-26</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Iraq_Sovereign_Model.xlsx
+++ b/models/sovereigns/Iraq_Sovereign_Model.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>as of 08-Oct-26</t>
+          <t>as of 09-Oct-26</t>
         </is>
       </c>
     </row>
@@ -716,12 +716,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026E</t>
+          <t>2026F</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IMF projections (as cited in adjudicated document)</t>
+          <t>IMF Projections</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Total public debt, projected year-end 2026 (approx.)</t>
+          <t>Total public debt, projected year-end</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>None (Article IV surveillance and Post-Financing Assessment; last SBA expired 2018)</t>
+          <t>None (Article IV surveillance and Post-Financing Assessment only; last SBA expired 2018)</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1343,6 +1343,11 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>2026F</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Source</t>
         </is>
       </c>
@@ -1356,7 +1361,8 @@
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="2" t="n"/>
       <c r="D2" s="2" t="n"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1369,9 +1375,12 @@
       <c r="D3" s="2" t="n">
         <v>-6.8</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>IMF projections, 20-May-25</t>
+      <c r="E3" s="2" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>IMF Projections, 20-May-25</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1393,8 @@
       <c r="B4" s="2" t="n"/>
       <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="n"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1395,7 +1405,8 @@
       <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="n"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1408,7 +1419,8 @@
       </c>
       <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="n"/>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" t="inlineStr">
         <is>
           <t>IMF Article IV, 20-May-25</t>
         </is>
@@ -1423,7 +1435,8 @@
       <c r="B7" s="2" t="n"/>
       <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="n"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1438,7 +1451,8 @@
       <c r="D8" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" t="inlineStr">
         <is>
           <t>IMF / Ministry of Finance, 31-Jul-26</t>
         </is>
@@ -1453,7 +1467,8 @@
       <c r="B9" s="2" t="n"/>
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1466,9 +1481,10 @@
         <v>97.40000000000001</v>
       </c>
       <c r="D10" s="2" t="n"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Central Bank of Iraq, 31-Jul-26 (end-2025 level)</t>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Central Bank of Iraq, 31-Jul-26 (end-2025 value)</t>
         </is>
       </c>
     </row>
@@ -1481,7 +1497,8 @@
       <c r="B11" s="2" t="n"/>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1492,7 +1509,8 @@
       <c r="B12" s="2" t="n"/>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/models/sovereigns/Iraq_Sovereign_Model.xlsx
+++ b/models/sovereigns/Iraq_Sovereign_Model.xlsx
@@ -716,12 +716,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026F</t>
+          <t>2026E</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IMF Projections</t>
+          <t>IMF Article IV projection</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>57</v>
+        <v>53.9</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026E</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Total public debt, projected year-end</t>
+          <t>Total public debt (IMF / Ministry of Finance); projected ~57% by end-2026</t>
         </is>
       </c>
     </row>
@@ -983,7 +983,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CBI gross official foreign exchange reserves</t>
+          <t>CBI gross international reserves (gross official foreign exchange reserves)</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Luxembourg Stock Exchange / Bondblox</t>
+          <t>Bondblox / Luxembourg Stock Exchange (USD 5.80% 2028, XS0240295575, amortising)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>IMF Projections, 20-May-25</t>
+          <t>IMF Article IV, 20-May-25</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,9 @@
       <c r="D8" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="E8" s="2" t="n"/>
+      <c r="E8" s="2" t="n">
+        <v>57</v>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>IMF / Ministry of Finance, 31-Jul-26</t>
@@ -1484,7 +1486,7 @@
       <c r="E10" s="2" t="n"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Central Bank of Iraq, 31-Jul-26 (end-2025 value)</t>
+          <t>Central Bank of Iraq (end-2025 gross reserves), 31-Jul-26</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Iraq_Sovereign_Model.xlsx
+++ b/models/sovereigns/Iraq_Sovereign_Model.xlsx
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>53.9</v>
+        <v>57</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026E</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Total public debt (IMF / Ministry of Finance); projected ~57% by end-2026</t>
+          <t>Total public debt, projected year-end 2026 (53.9% in 2025)</t>
         </is>
       </c>
     </row>
@@ -983,7 +983,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CBI gross international reserves (gross official foreign exchange reserves)</t>
+          <t>CBI gross official foreign exchange reserves</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bondblox / Luxembourg Stock Exchange (USD 5.80% 2028, XS0240295575, amortising)</t>
+          <t>Bondblox / Luxembourg Stock Exchange (USD 5.80% 2028, amortising)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>None (Article IV surveillance and Post-Financing Assessment only; last SBA expired 2018)</t>
+          <t>None active (Article IV surveillance and Post-Financing Assessment; last SBA expired 2018)</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       <c r="E10" s="2" t="n"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Central Bank of Iraq (end-2025 gross reserves), 31-Jul-26</t>
+          <t>Central Bank of Iraq (end-2025), 31-Jul-26</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Iraq_Sovereign_Model.xlsx
+++ b/models/sovereigns/Iraq_Sovereign_Model.xlsx
@@ -721,7 +721,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IMF Article IV projection</t>
+          <t>IMF projections (Article IV)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>57</v>
+        <v>53.9</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026E</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Total public debt, projected year-end 2026 (53.9% in 2025)</t>
+          <t>Total public debt to GDP</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Central Bank of Iraq</t>
+          <t>Central Bank of Iraq Monthly Statistical Bulletin</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1137,12 +1137,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Oct-26</t>
+          <t>08-Oct-26</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bondblox / Luxembourg Stock Exchange (USD 5.80% 2028, amortising)</t>
+          <t>Luxembourg Stock Exchange / Bondblox (USD 5.80% 2028, ISIN XS0240295575)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1295,11 +1295,6 @@
       <c r="A33" t="inlineStr">
         <is>
           <t>IMF</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>None active (Article IV surveillance and Post-Financing Assessment; last SBA expired 2018)</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1375,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>IMF Article IV, 20-May-25</t>
+          <t>IMF Article IV projections, 20-May-25</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1451,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>IMF / Ministry of Finance, 31-Jul-26</t>
+          <t>IMF / Ministry of Finance, 31-Jul-26 (2026F is a projection)</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1481,7 @@
       <c r="E10" s="2" t="n"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Central Bank of Iraq (end-2025), 31-Jul-26</t>
+          <t>Central Bank of Iraq, end-2025 value cited 31-Jul-26</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Iraq_Sovereign_Model.xlsx
+++ b/models/sovereigns/Iraq_Sovereign_Model.xlsx
@@ -721,7 +721,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IMF projections (Article IV)</t>
+          <t>IMF Article IV projection</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Central Bank of Iraq Monthly Statistical Bulletin</t>
+          <t>Central Bank of Iraq, Monthly Statistical Bulletin</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Luxembourg Stock Exchange / Bondblox (USD 5.80% 2028, ISIN XS0240295575)</t>
+          <t>Luxembourg Stock Exchange / Bondblox (USD 5.80% 2028, XS0240295575, amortising)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1295,6 +1295,11 @@
       <c r="A33" t="inlineStr">
         <is>
           <t>IMF</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>None active (Article IV surveillance and Post-Financing Assessment; last SBA expired 2018)</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1380,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>IMF Article IV projections, 20-May-25</t>
+          <t>IMF Article IV projection, 20-May-25</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1456,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>IMF / Ministry of Finance, 31-Jul-26 (2026F is a projection)</t>
+          <t>IMF / Ministry of Finance, 31-Jul-26 (2026E is approximate, ~57%)</t>
         </is>
       </c>
     </row>
@@ -1481,7 +1486,7 @@
       <c r="E10" s="2" t="n"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Central Bank of Iraq, end-2025 value cited 31-Jul-26</t>
+          <t>Central Bank of Iraq, end-2025 level cited 31-Jul-26</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Iraq_Sovereign_Model.xlsx
+++ b/models/sovereigns/Iraq_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/iraq.json</t>
+          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/iraq.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Iraq_Sovereign_Model.xlsx
+++ b/models/sovereigns/Iraq_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/iraq.json</t>
+          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/iraq.json</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>3.0928</v>
+        <v>1.5009</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>19-Oct-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">

--- a/models/sovereigns/Iraq_Sovereign_Model.xlsx
+++ b/models/sovereigns/Iraq_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/iraq.json</t>
+          <t>built 26-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/iraq.json</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1.5009</v>
+        <v>3.2588</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>19-Oct-26</t>
+          <t>26-Oct-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
